--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\RAFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854BB8CD-A486-45EC-9C68-C1D5F236C6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BBEBE0-0D98-412C-9A41-965ED42C89A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57600" yWindow="5085" windowWidth="66150" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -109,6 +109,24 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>TbCharacterJob</t>
+  </si>
+  <si>
+    <t>CharacterJob</t>
+  </si>
+  <si>
+    <t>CharacterJob.xlsx</t>
+  </si>
+  <si>
+    <t>JobId</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>职业配置表（结构在 Defines/character.xml，字段带 group 区分客户端/服务端）</t>
   </si>
 </sst>
 </file>
@@ -212,7 +230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -241,6 +259,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -530,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -677,6 +701,29 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
+    <row r="10" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BBEBE0-0D98-412C-9A41-965ED42C89A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD835BE-DE9D-4469-92E0-B4A8CDC89CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,40 @@
   </si>
   <si>
     <t>职业配置表（结构在 Defines/character.xml，字段带 group 区分客户端/服务端）</t>
+  </si>
+  <si>
+    <t>TbJobSpecialization</t>
+  </si>
+  <si>
+    <t>JobSpecialization</t>
+  </si>
+  <si>
+    <t>JobSpecialization.xlsx</t>
+  </si>
+  <si>
+    <t>SpecId</t>
+  </si>
+  <si>
+    <t>专职表（结构在 Defines/character.xml）</t>
+  </si>
+  <si>
+    <t>TbSpecializationForm</t>
+  </si>
+  <si>
+    <t>SpecializationForm</t>
+  </si>
+  <si>
+    <t>SpecializationForm.xlsx</t>
+  </si>
+  <si>
+    <t>SpecId+Stage</t>
+  </si>
+  <si>
+    <t>专职形态表，联合主键 SpecId+Stage（结构在 Defines/character.xml）</t>
+  </si>
+  <si>
+    <t>list</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -554,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -724,6 +758,52 @@
         <v>32</v>
       </c>
     </row>
+    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD835BE-DE9D-4469-92E0-B4A8CDC89CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAE24C0-50CE-4058-94A1-DEB05A16205C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6320" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -126,40 +126,33 @@
     <t>map</t>
   </si>
   <si>
-    <t>职业配置表（结构在 Defines/character.xml，字段带 group 区分客户端/服务端）</t>
-  </si>
-  <si>
-    <t>TbJobSpecialization</t>
-  </si>
-  <si>
-    <t>JobSpecialization</t>
-  </si>
-  <si>
-    <t>JobSpecialization.xlsx</t>
-  </si>
-  <si>
-    <t>SpecId</t>
-  </si>
-  <si>
-    <t>专职表（结构在 Defines/character.xml）</t>
-  </si>
-  <si>
-    <t>TbSpecializationForm</t>
-  </si>
-  <si>
-    <t>SpecializationForm</t>
-  </si>
-  <si>
-    <t>SpecializationForm.xlsx</t>
-  </si>
-  <si>
-    <t>SpecId+Stage</t>
-  </si>
-  <si>
-    <t>专职形态表，联合主键 SpecId+Stage（结构在 Defines/character.xml）</t>
+    <t>TbCharacterForm</t>
+  </si>
+  <si>
+    <t>CharacterForm</t>
+  </si>
+  <si>
+    <t>CharacterForm.xlsx</t>
+  </si>
+  <si>
+    <t>JobId+FormId</t>
   </si>
   <si>
     <t>list</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>True</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色/职业表。结构和分组都看 CharacterJob.xlsx 的表头（read_schema_from_file=True）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色形态表，联合主键 JobId+FormId。基础线(FormType=1)按星级现算当前形态，爆发线(FormType=2)一个角色可多个。结构看 CharacterForm.xlsx 表头</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -742,8 +735,8 @@
       <c r="C10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3" t="b">
-        <v>0</v>
+      <c r="D10" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>29</v>
@@ -755,53 +748,30 @@
         <v>31</v>
       </c>
       <c r="I10" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="84" x14ac:dyDescent="0.3">
+      <c r="B11" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="I11" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="42" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAE24C0-50CE-4058-94A1-DEB05A16205C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DAEA22-E3AE-4673-877E-642933EDBBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6320" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5040" windowWidth="47520" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -154,6 +154,36 @@
   <si>
     <t>角色形态表，联合主键 JobId+FormId。基础线(FormType=1)按星级现算当前形态，爆发线(FormType=2)一个角色可多个。结构看 CharacterForm.xlsx 表头</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbTown</t>
+  </si>
+  <si>
+    <t>Town</t>
+  </si>
+  <si>
+    <t>Town.xlsx</t>
+  </si>
+  <si>
+    <t>TownId</t>
+  </si>
+  <si>
+    <t>城镇表。结构和分组看 Town.xlsx 表头。三列背景控制器对应早/中/晚三个时段</t>
+  </si>
+  <si>
+    <t>TbTimeBand</t>
+  </si>
+  <si>
+    <t>TimeBand</t>
+  </si>
+  <si>
+    <t>TimeBand.xlsx</t>
+  </si>
+  <si>
+    <t>BandId</t>
+  </si>
+  <si>
+    <t>时间段表。段数固定3段(早/中/晚)，只有边界(StartHour)可调</t>
   </si>
 </sst>
 </file>
@@ -581,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -774,6 +804,52 @@
         <v>40</v>
       </c>
     </row>
+    <row r="12" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DAEA22-E3AE-4673-877E-642933EDBBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09908911-4A76-4D1E-86E8-38EEF999AC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5040" windowWidth="47520" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3550" windowWidth="51320" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -184,6 +184,21 @@
   </si>
   <si>
     <t>时间段表。段数固定3段(早/中/晚)，只有边界(StartHour)可调</t>
+  </si>
+  <si>
+    <t>TbLevelExp</t>
+  </si>
+  <si>
+    <t>LevelExp</t>
+  </si>
+  <si>
+    <t>LevelExp.xlsx</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>等级表。升级所需经验 + 该等级的体力上限(每日重置)。经验条和体力条的分母都来自这里</t>
   </si>
 </sst>
 </file>
@@ -611,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -850,6 +865,29 @@
         <v>50</v>
       </c>
     </row>
+    <row r="14" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="B14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09908911-4A76-4D1E-86E8-38EEF999AC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304431CD-E001-4C43-9B45-9FF3638C279D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3550" windowWidth="51320" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -199,6 +199,24 @@
   </si>
   <si>
     <t>等级表。升级所需经验 + 该等级的体力上限(每日重置)。经验条和体力条的分母都来自这里</t>
+  </si>
+  <si>
+    <t>TbTownNpc</t>
+  </si>
+  <si>
+    <t>TownNpc</t>
+  </si>
+  <si>
+    <t>TownNpc.xlsx</t>
+  </si>
+  <si>
+    <t>NpcId</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>城镇NPC表。一行一个NPC，站在某个城镇的固定世界坐标上。纯客户端表现，服务端没有NPC概念。结构看 TownNpc.xlsx 表头（read_schema_from_file=True）</t>
   </si>
 </sst>
 </file>
@@ -626,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -888,6 +906,32 @@
         <v>55</v>
       </c>
     </row>
+    <row r="15" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+      <c r="B15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304431CD-E001-4C43-9B45-9FF3638C279D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE0BD19-DDC5-4888-AEA5-60F7C4D1F832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -217,6 +217,21 @@
   </si>
   <si>
     <t>城镇NPC表。一行一个NPC，站在某个城镇的固定世界坐标上。纯客户端表现，服务端没有NPC概念。结构看 TownNpc.xlsx 表头（read_schema_from_file=True）</t>
+  </si>
+  <si>
+    <t>TbTownTrigger</t>
+  </si>
+  <si>
+    <t>TownTrigger</t>
+  </si>
+  <si>
+    <t>TownTrigger.xlsx</t>
+  </si>
+  <si>
+    <t>TriggerId</t>
+  </si>
+  <si>
+    <t>城镇触发器表。一行一个矩形触发区，玩家走进去就生效：Kind=1 传送到别的城镇（走服务端 ChangeTown），Kind=2 打开副本界面。纯客户端表现，服务端不认识触发器（能不能去哪个城镇由服务端自己校验）。结构看 TownTrigger.xlsx 表头（read_schema_from_file=True）</t>
   </si>
 </sst>
 </file>
@@ -644,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -932,6 +947,32 @@
         <v>61</v>
       </c>
     </row>
+    <row r="16" spans="1:11" ht="126" x14ac:dyDescent="0.3">
+      <c r="B16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE0BD19-DDC5-4888-AEA5-60F7C4D1F832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2DFDA9-6ECC-4177-96B8-60B865FF8614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -232,6 +232,36 @@
   </si>
   <si>
     <t>城镇触发器表。一行一个矩形触发区，玩家走进去就生效：Kind=1 传送到别的城镇（走服务端 ChangeTown），Kind=2 打开副本界面。纯客户端表现，服务端不认识触发器（能不能去哪个城镇由服务端自己校验）。结构看 TownTrigger.xlsx 表头（read_schema_from_file=True）</t>
+  </si>
+  <si>
+    <t>TbDungeonArea</t>
+  </si>
+  <si>
+    <t>DungeonArea</t>
+  </si>
+  <si>
+    <t>DungeonArea.xlsx</t>
+  </si>
+  <si>
+    <t>AreaId</t>
+  </si>
+  <si>
+    <t>副本区域表(像DNF的格兰之森)。一个区域下面挂多个小副本，区域自己带一张背景。城镇触发器Kind=2的TargetId指的就是AreaId。纯客户端表现，服务端不认识副本。结构看 DungeonArea.xlsx 表头</t>
+  </si>
+  <si>
+    <t>TbDungeon</t>
+  </si>
+  <si>
+    <t>Dungeon</t>
+  </si>
+  <si>
+    <t>Dungeon.xlsx</t>
+  </si>
+  <si>
+    <t>DungeonId</t>
+  </si>
+  <si>
+    <t>小副本表。一行一个副本(界面上一个格子)，MaxStar是配置允许的最高挑战星级，实际能选到几星还要看通关进度。纯客户端，等做进副本/结算时再把要校验的列开给服务端。结构看 Dungeon.xlsx 表头</t>
   </si>
 </sst>
 </file>
@@ -659,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -973,6 +1003,58 @@
         <v>66</v>
       </c>
     </row>
+    <row r="17" spans="2:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="B17" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="B18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
